--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.59585387911752</v>
+        <v>9.034326255356598</v>
       </c>
       <c r="D2" t="n">
-        <v>55.23204296851731</v>
+        <v>8.975206982384064</v>
       </c>
       <c r="E2" t="n">
-        <v>17.87668246012612</v>
+        <v>2.904960899770494</v>
       </c>
       <c r="F2" t="n">
-        <v>17.62665785654214</v>
+        <v>2.864331901688098</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.7073002759561</v>
+        <v>7.589936294842866</v>
       </c>
       <c r="D3" t="n">
-        <v>46.34968728935367</v>
+        <v>7.531824184519972</v>
       </c>
       <c r="E3" t="n">
-        <v>17.87668246012612</v>
+        <v>2.904960899770494</v>
       </c>
       <c r="F3" t="n">
-        <v>17.62665785654214</v>
+        <v>2.864331901688098</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>75.63154398960231</v>
+        <v>12.29012589831038</v>
       </c>
       <c r="D4" t="n">
-        <v>75.48785535707314</v>
+        <v>12.26677649552439</v>
       </c>
       <c r="E4" t="n">
-        <v>17.87668246012612</v>
+        <v>2.904960899770494</v>
       </c>
       <c r="F4" t="n">
-        <v>17.62665785654214</v>
+        <v>2.864331901688098</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.12615332168206</v>
+        <v>9.770499914773335</v>
       </c>
       <c r="D5" t="n">
-        <v>60.28613289222422</v>
+        <v>9.796496594986436</v>
       </c>
       <c r="E5" t="n">
-        <v>17.87668246012612</v>
+        <v>2.904960899770494</v>
       </c>
       <c r="F5" t="n">
-        <v>17.62665785654214</v>
+        <v>2.864331901688098</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.52414310112007</v>
+        <v>3.822673253932012</v>
       </c>
       <c r="D6" t="n">
-        <v>23.58187229324043</v>
+        <v>3.83205424765157</v>
       </c>
       <c r="E6" t="n">
-        <v>17.87668246012612</v>
+        <v>2.904960899770494</v>
       </c>
       <c r="F6" t="n">
-        <v>17.62665785654214</v>
+        <v>2.864331901688098</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.29555858976612</v>
+        <v>4.760528270836994</v>
       </c>
       <c r="D7" t="n">
-        <v>30.44165640112976</v>
+        <v>4.946769165183586</v>
       </c>
       <c r="E7" t="n">
-        <v>17.87668246012612</v>
+        <v>2.904960899770494</v>
       </c>
       <c r="F7" t="n">
-        <v>17.62665785654214</v>
+        <v>2.864331901688098</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
